--- a/plantilla.xlsx
+++ b/plantilla.xlsx
@@ -1,28 +1,54 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose.gago\Desktop\simulador poc\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A00D01-6DB7-445D-AE94-F896022001CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="INPUTS" sheetId="1" r:id="rId1"/>
+    <sheet name="OUTPUTS" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="72"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,8 +75,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +359,40 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45BDDBFC-8E73-4ED9-A7A1-49599AEE02B2}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="92.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="1">
+        <f>INPUTS!A1+INPUTS!A2</f>
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/plantilla.xlsx
+++ b/plantilla.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose.gago\Desktop\simulador poc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A00D01-6DB7-445D-AE94-F896022001CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{875055C6-C38E-44DC-8CAC-F99DC1702E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -365,12 +365,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -389,7 +389,7 @@
     <row r="1" spans="1:1" ht="92.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1">
         <f>INPUTS!A1+INPUTS!A2</f>
-        <v>57</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
